--- a/config/categories.xlsx
+++ b/config/categories.xlsx
@@ -103,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -131,6 +131,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -592,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -643,11 +644,11 @@
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="7" t="n">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>スキンケア全般</t>
+          <t>スキンケア・基礎化粧品</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -674,7 +675,7 @@
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="9" t="n">
-        <v>102</v>
+        <v>900</v>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
@@ -705,16 +706,16 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="9" t="n">
-        <v>103</v>
+        <v>901</v>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>化粧水</t>
+          <t>クレンジング</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>toner_lotion</t>
+          <t>cleansing</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -730,22 +731,22 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Core hypothesis category</t>
+          <t>Makeup remover / cleansing oil — @cosme splits this from 洗顔料 (900)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="9" t="n">
-        <v>104</v>
+        <v>902</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>乳液</t>
+          <t>化粧水</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>emulsion</t>
+          <t>toner_lotion</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -759,20 +760,24 @@
       <c r="F5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="10" t="inlineStr"/>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Core hypothesis category</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="9" t="n">
-        <v>105</v>
+        <v>1004</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>クリーム</t>
+          <t>乳液</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>face_cream</t>
+          <t>emulsion</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -790,16 +795,16 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="9" t="n">
-        <v>106</v>
+        <v>1005</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>美容液</t>
+          <t>フェイスクリーム</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>serum_essence</t>
+          <t>face_cream</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -813,24 +818,20 @@
       <c r="F7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>High ingredient literacy — primary NLP discovery category</t>
-        </is>
-      </c>
+      <c r="G7" s="10" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="9" t="n">
-        <v>113</v>
+        <v>1006</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>日焼け止め</t>
+          <t>美容液</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>sun_protection</t>
+          <t>serum_essence</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -846,27 +847,27 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Anessa dominant — Shiseido/UV signal</t>
+          <t>High ingredient literacy — primary NLP discovery category</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="9" t="n">
-        <v>201</v>
+        <v>1037</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>ファンデーション</t>
+          <t>日焼け止め・UVケア(顔用)</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>sun_protection</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>cosmetics</t>
+          <t>skincare</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -877,22 +878,22 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Core hypothesis category</t>
+          <t>Anessa dominant — Shiseido/UV signal</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="9" t="n">
-        <v>205</v>
+        <v>916</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>口紅・リップ</t>
+          <t>ファンデーション</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>lip_colour</t>
+          <t>foundation</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -906,34 +907,65 @@
       <c r="F10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="10" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Core hypothesis category</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="9" t="n">
-        <v>208</v>
+        <v>913</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
+          <t>口紅・グロス・リップライナー</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>lip_colour</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>cosmetics</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>912</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
           <t>アイシャドウ</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>eye_shadow</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>cosmetics</t>
         </is>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="10" t="inlineStr"/>
+      <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
